--- a/marketing_forms/025_volume_preferences_survey--marketing_forms.xlsx
+++ b/marketing_forms/025_volume_preferences_survey--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales_data'}</t>
+          <t>sales_data</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales Data'}</t>
+          <t>Sales Data</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'order_data'}</t>
+          <t>order_data</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Order Data'}</t>
+          <t>Order Data</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'enterprise'}</t>
+          <t>enterprise</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Enterprise'}</t>
+          <t>Enterprise</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'small_business'}</t>
+          <t>small_business</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Small Business'}</t>
+          <t>Small Business</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'crm'}</t>
+          <t>crm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'CRM'}</t>
+          <t>CRM</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'erp'}</t>
+          <t>erp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'ERP'}</t>
+          <t>ERP</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'database'}</t>
+          <t>database</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Database'}</t>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'automated'}</t>
+          <t>automated</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Automated'}</t>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales_manager'}</t>
+          <t>sales_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales Manager'}</t>
+          <t>Sales Manager</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'account_manager'}</t>
+          <t>account_manager</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Account Manager'}</t>
+          <t>Account Manager</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales_manager'}</t>
+          <t>sales_manager</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales Manager'}</t>
+          <t>Sales Manager</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'account_manager'}</t>
+          <t>account_manager</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Account Manager'}</t>
+          <t>Account Manager</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales_manager'}</t>
+          <t>sales_manager</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales Manager'}</t>
+          <t>Sales Manager</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'account_manager'}</t>
+          <t>account_manager</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Account Manager'}</t>
+          <t>Account Manager</t>
         </is>
       </c>
     </row>
